--- a/data/S1988_89_FINAL.xlsx
+++ b/data/S1988_89_FINAL.xlsx
@@ -27,8 +27,11 @@
     <sheet name="SERIES" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="CLUBS" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="META" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$55</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -36,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,8 +54,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +81,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -87,12 +99,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -23722,7 +23740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23798,6 +23816,664 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1988_89_0413 'Rájec-Jestřebí' prev→CLUB_S1987_88_0416 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0049 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0050 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0051 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0052 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0053 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0054 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0055 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0056 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0057 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0102 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0103 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0104 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0107 fate nekonzist. ['setrval', 'setrval?'] → 'setrval' (cross-ref=ne) — ověřit</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0108 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0109 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0175 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0176 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0177 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0178 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0401 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0402 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0403 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0404 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0405 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0406 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0408 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0409 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0410 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0412 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0413 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0414 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0415 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0416 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0418 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0419 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0420 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0421 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0422 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0451 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0452 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0453 fate nekonzist. ['setrval', 'setrval?'] → 'setrval' (cross-ref=ne) — ověřit</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0454 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0462 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0463 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0464 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0465 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0466 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0467 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0468 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0469 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1988_89_0470 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0002</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1988_89_0002 'Kvalifikace o 1.CHL' (L15, parent=NODE_S1988_89_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0018</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1988_89_0018 'Prolínací soutěž' (L15, parent=NODE_S1988_89_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -29394,8 +30070,6 @@
         </is>
       </c>
     </row>
-    <row r="133"/>
-    <row r="134"/>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
@@ -29475,7 +30149,6 @@
         </is>
       </c>
     </row>
-    <row r="142"/>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
@@ -57502,6 +58175,1249 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0413</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0413 'Rájec-Jestřebí' prev→CLUB_S1987_88_0416 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0049</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0049 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0050</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0050 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0051</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0051 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0052</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0052 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0053</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0053 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0054</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0054 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0055</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0055 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0056</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0056 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0057</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0057 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0102</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0102 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0103</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0103 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0104</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0104 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0107</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0107 fate nekonzist. ['setrval', 'setrval?'] → 'setrval' (cross-ref=ne) — ověřit</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0108</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0108 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0109</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0109 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0175</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0175 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0176</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0176 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0177</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0177 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0178</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0178 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0401</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0401 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0402</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0402 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0403</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0403 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0404</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0404 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0405</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0405 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0406</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0406 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0408</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0408 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0409</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0409 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0410</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0410 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0412</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0412 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0413</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0413 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0414</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0414 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0415</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0415 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0416</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0416 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0418</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0418 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0419</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0419 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0420</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0420 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0421</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0421 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0422</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0422 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0451</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0451 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0452</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0452 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0453</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0453 fate nekonzist. ['setrval', 'setrval?'] → 'setrval' (cross-ref=ne) — ověřit</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0454</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0454 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0462</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0462 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0463</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0463 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0464</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0464 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0465</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0465 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0466</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0466 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0467</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0467 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0468</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0468 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0469</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0469 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0470</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0470 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0002</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1988_89_0002 'Kvalifikace o 1.CHL' (L15, parent=NODE_S1988_89_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0018</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1988_89_0018 'Prolínací soutěž' (L15, parent=NODE_S1988_89_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F55"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1988_89_FINAL.xlsx
+++ b/data/S1988_89_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$66</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23740,7 +23740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23822,7 +23822,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1988_89_0413 'Rájec-Jestřebí' prev→CLUB_S1987_88_0416 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -23834,7 +23834,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0049 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -23846,7 +23846,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0050 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -23858,7 +23858,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0051 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -23870,7 +23870,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0052 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -23882,7 +23882,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0053 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -23894,7 +23894,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0054 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -23906,7 +23906,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0055 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -23918,7 +23918,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0056 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -23930,7 +23930,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0057 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -23942,7 +23942,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0102 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -23954,7 +23954,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0103 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -23966,7 +23966,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0104 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -23978,7 +23978,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0107 fate nekonzist. ['setrval', 'setrval?'] → 'setrval' (cross-ref=ne) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -23990,7 +23990,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0108 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -24002,7 +24002,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0109 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -24014,7 +24014,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0175 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -24026,7 +24026,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0176 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -24038,7 +24038,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0177 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -24050,7 +24050,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0178 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -24062,7 +24062,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0401 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -24074,7 +24074,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0402 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -24086,7 +24086,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0403 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -24098,7 +24098,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0404 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -24110,7 +24110,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0405 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -24122,7 +24122,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0406 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -24134,7 +24134,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0408 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -24146,7 +24146,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0409 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -24158,7 +24158,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0410 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -24170,7 +24170,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0412 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1987_88_0216 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -24182,7 +24182,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0413 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kluky' → 'Dražice A' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -24194,7 +24194,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0414 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -24206,7 +24206,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0415 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Stadion Cheb' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -24218,7 +24218,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0416 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -24230,7 +24230,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0418 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -24242,7 +24242,7 @@
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0419 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -24254,7 +24254,7 @@
     <row r="40">
       <c r="C40" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0420 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Centroflor Dolní Pustevna' → 'Dolní Pustevna' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -24266,7 +24266,7 @@
     <row r="41">
       <c r="C41" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0421 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -24278,7 +24278,7 @@
     <row r="42">
       <c r="C42" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0422 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -24290,7 +24290,7 @@
     <row r="43">
       <c r="C43" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0451 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -24302,7 +24302,7 @@
     <row r="44">
       <c r="C44" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0452 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -24314,7 +24314,7 @@
     <row r="45">
       <c r="C45" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0453 fate nekonzist. ['setrval', 'setrval?'] → 'setrval' (cross-ref=ne) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -24326,7 +24326,7 @@
     <row r="46">
       <c r="C46" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0454 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -24338,7 +24338,7 @@
     <row r="47">
       <c r="C47" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0462 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -24350,7 +24350,7 @@
     <row r="48">
       <c r="C48" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0463 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -24362,7 +24362,7 @@
     <row r="49">
       <c r="C49" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0464 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -24374,7 +24374,7 @@
     <row r="50">
       <c r="C50" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0465 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -24386,7 +24386,7 @@
     <row r="51">
       <c r="C51" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0466 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -24398,7 +24398,7 @@
     <row r="52">
       <c r="C52" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0467 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -24410,7 +24410,7 @@
     <row r="53">
       <c r="C53" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0468 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -24422,7 +24422,7 @@
     <row r="54">
       <c r="C54" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0469 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -24434,7 +24434,7 @@
     <row r="55">
       <c r="C55" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1988_89_0470 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -24444,14 +24444,9 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>NODE_S1988_89_0002</t>
-        </is>
-      </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1988_89_0002 'Kvalifikace o 1.CHL' (L15, parent=NODE_S1988_89_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -24461,17 +24456,159 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>NODE_S1988_89_0018</t>
-        </is>
-      </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1988_89_0018 'Prolínací soutěž' (L15, parent=NODE_S1988_89_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1987_88_0451 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1987_88_0416 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hutní Montáže Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Jednota SD Brezno' → 'Brezno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Štátný majetok Poprad' → 'Poprad' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0027</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0028</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0029</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -30070,6 +30207,8 @@
         </is>
       </c>
     </row>
+    <row r="133"/>
+    <row r="134"/>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
@@ -30100,6 +30239,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0001</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -30112,6 +30256,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0003</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -30124,6 +30273,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0003</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -30136,6 +30290,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0038</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -30149,6 +30308,7 @@
         </is>
       </c>
     </row>
+    <row r="142"/>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
@@ -32593,12 +32753,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -33191,12 +33351,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -33359,12 +33519,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -33443,12 +33603,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -33784,12 +33944,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Kolora Liberec</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -33915,12 +34075,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom.</t>
+          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom. || TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>SMZ Dubnica nad Váhom</t>
+          <t>Dubnica nad Váhom</t>
         </is>
       </c>
     </row>
@@ -34661,12 +34821,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor.</t>
+          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor. || TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor</t>
+          <t>Tábor</t>
         </is>
       </c>
     </row>
@@ -34750,12 +34910,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -34792,12 +34952,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -34834,12 +34994,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha.</t>
+          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha. || TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>DP I. ČLTK Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -35054,12 +35214,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha.</t>
+          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha. || TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Uhelné sklady Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -35138,12 +35298,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov.</t>
+          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov. || TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>VVŠ PV Vyškov</t>
+          <t>Vyškov</t>
         </is>
       </c>
     </row>
@@ -35657,12 +35817,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Nové Zámky = TJ Lokomotiva Nové Zámky (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. Železničárský klub. Patterns: Lokomotíva Nové Zámky -&gt; Lokomotiva Nové Zámky. city Nové Zámky.</t>
+          <t>Nové Zámky = TJ Lokomotiva Nové Zámky (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. Železničárský klub. Patterns: Lokomotíva Nové Zámky -&gt; Lokomotiva Nové Zámky. city Nové Zámky. || TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Lokomotiva Nové Zámky</t>
+          <t>Nové Zámky</t>
         </is>
       </c>
     </row>
@@ -35951,12 +36111,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -36114,12 +36274,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -36203,12 +36363,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -37152,12 +37312,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr.</t>
+          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr. || TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>KŽ Králův Dvůr</t>
+          <t>Králův Dvůr</t>
         </is>
       </c>
     </row>
@@ -39536,12 +39696,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -39620,12 +39780,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -39662,12 +39822,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -39704,12 +39864,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -39793,12 +39953,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -40107,12 +40267,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -40347,12 +40507,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá. || TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Smrčina Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -40582,12 +40742,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -40676,12 +40836,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -40723,12 +40883,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -40864,12 +41024,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -42974,12 +43134,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Kluky u Písku = TJ Sokol Kluky (Wiki D42 - registr ustavy 04/2026). 'Sokol  Kluky' s dvojite mezerou - parsing artifakt. Jihocesky kraj (okres Pisek). city Kluky u Písku.</t>
+          <t>Kluky u Písku = TJ Sokol Kluky (Wiki D42 - registr ustavy 04/2026). 'Sokol  Kluky' s dvojite mezerou - parsing artifakt. Jihocesky kraj (okres Pisek). city Kluky u Písku. || TBD: city 'Kluky' → 'Dražice A' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Kluky</t>
+          <t>Dražice A</t>
         </is>
       </c>
     </row>
@@ -43614,12 +43774,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu.</t>
+          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu. || TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Start VD Luby</t>
+          <t>Luby</t>
         </is>
       </c>
     </row>
@@ -43918,12 +44078,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Stadion Cheb' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Stadion Cheb</t>
         </is>
       </c>
     </row>
@@ -44546,12 +44706,12 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -44635,12 +44795,12 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou = TJ Bižuterie Jablonec (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Bižuterie Jablonec** = sklarsky podnik (svetove znamy vyrobce bizutérie). city Jablonec nad Nisou.</t>
+          <t>Jablonec nad Nisou = TJ Bižuterie Jablonec (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Bižuterie Jablonec** = sklarsky podnik (svetove znamy vyrobce bizutérie). city Jablonec nad Nisou. || TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>Bižuterie Jablonec</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -44813,12 +44973,12 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -44949,12 +45109,12 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>Dolní Poustevna = TJ Centroflor Dolní Poustevna (Wiki D42 - registr ustavy 04/2026). PARSING CHYBA: 'Pustevna' = preklep z 'Poustevna'. Severocesky/Ustecky kraj (okres Decin). city Dolní Poustevna.</t>
+          <t>Dolní Poustevna = TJ Centroflor Dolní Poustevna (Wiki D42 - registr ustavy 04/2026). PARSING CHYBA: 'Pustevna' = preklep z 'Poustevna'. Severocesky/Ustecky kraj (okres Decin). city Dolní Poustevna. || TBD: city 'Centroflor Dolní Pustevna' → 'Dolní Pustevna' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>Centroflor Dolní Pustevna</t>
+          <t>Dolní Pustevna</t>
         </is>
       </c>
     </row>
@@ -44996,12 +45156,12 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>Nový Bor = TJ Crystalex 08 Nový Bor (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Ceska Lipa). **Crystalex** = svetove znama sklarna (drive Crystalex Nový Bor, dnes pod Crystalex CZ). **Nový Bor = sklarsky mesto**. city Nový Bor.</t>
+          <t>Nový Bor = TJ Crystalex 08 Nový Bor (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Ceska Lipa). **Crystalex** = svetove znama sklarna (drive Crystalex Nový Bor, dnes pod Crystalex CZ). **Nový Bor = sklarsky mesto**. city Nový Bor. || TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>Crystalex 08 Nový Bor</t>
+          <t>Nový Bor</t>
         </is>
       </c>
     </row>
@@ -45043,12 +45203,12 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>Nový Bor = TJ Crystalex 08 Nový Bor (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Ceska Lipa). **Crystalex** = svetove znama sklarna (drive Crystalex Nový Bor, dnes pod Crystalex CZ). **Nový Bor = sklarsky mesto**. city Nový Bor.</t>
+          <t>Nový Bor = TJ Crystalex 08 Nový Bor (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Ceska Lipa). **Crystalex** = svetove znama sklarna (drive Crystalex Nový Bor, dnes pod Crystalex CZ). **Nový Bor = sklarsky mesto**. city Nový Bor. || TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>Crystalex 08 Nový Bor</t>
+          <t>Nový Bor</t>
         </is>
       </c>
     </row>
@@ -45189,12 +45349,12 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -45236,12 +45396,12 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>Hrádek nL Nisou = TJ ČSAD Hrádek nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Liberec). **ČSAD** = Československá státní automobilová doprava. **Hrádek nL Nisou** = pohranicni mesto trojmezi (CR-DDR/Polsko-NSR). city Hrádek nad Nisou.</t>
+          <t>Hrádek nL Nisou = TJ ČSAD Hrádek nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Liberec). **ČSAD** = Československá státní automobilová doprava. **Hrádek nL Nisou** = pohranicni mesto trojmezi (CR-DDR/Polsko-NSR). city Hrádek nad Nisou. || TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>ČSAD Hrádek nad Nisou</t>
+          <t>Hrádek nad Nisou</t>
         </is>
       </c>
     </row>
@@ -45283,12 +45443,12 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -45424,12 +45584,12 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -45659,12 +45819,12 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -46890,12 +47050,12 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov.</t>
+          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov. || TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>Tepna ČKD Hronov</t>
+          <t>Hronov</t>
         </is>
       </c>
     </row>
@@ -49031,12 +49191,12 @@
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>Olomouc</t>
+          <t>Modeta Jihlava</t>
         </is>
       </c>
     </row>
@@ -49251,12 +49411,12 @@
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -49933,12 +50093,12 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>Veverská Bítýška = TJ RICO Veverská Bítýška (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov). **RICO** = pojmenovani po vyrobci (rychlosvyrabne ucely?). NE Veverí (mestska cast Brna), NE Bystřice u Veveří. city Veverská Bítýška.</t>
+          <t>Veverská Bítýška = TJ RICO Veverská Bítýška (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov). **RICO** = pojmenovani po vyrobci (rychlosvyrabne ucely?). NE Veverí (mestska cast Brna), NE Bystřice u Veveří. city Veverská Bítýška. || TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>RICO Veverská Bítýška</t>
+          <t>Veverská Bítýška</t>
         </is>
       </c>
     </row>
@@ -50368,12 +50528,12 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -51654,12 +51814,12 @@
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>Frýdek-Místek = TJ Slezan Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Slezan** = textilni podnik. Patterns: TJ Slezan Frýdek-Místek (z 80/81). city Frýdek-Místek.</t>
+          <t>Frýdek-Místek = TJ Slezan Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Slezan** = textilni podnik. Patterns: TJ Slezan Frýdek-Místek (z 80/81). city Frýdek-Místek. || TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>Slezan Frýdek Místek</t>
+          <t>Frýdek Místek</t>
         </is>
       </c>
     </row>
@@ -51738,12 +51898,12 @@
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>Ostrava = TJ Hutní Montáže Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. Patterns: HM Ostrava. city Ostrava.</t>
+          <t>Ostrava = TJ Hutní Montáže Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. Patterns: HM Ostrava. city Ostrava. || TBD: city 'Hutní Montáže Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>Hutní Montáže Ostrava</t>
+          <t>Ostrava</t>
         </is>
       </c>
     </row>
@@ -51822,12 +51982,12 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -54081,12 +54241,12 @@
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t>Brezno = TJ Jednota SD Brezno (Wiki D42 - registr ustavy 04/2026). Slovensky/Banskobystricky kraj. **Jednota SD** = Spotrebné družstvo Jednota. city Brezno.</t>
+          <t>Brezno = TJ Jednota SD Brezno (Wiki D42 - registr ustavy 04/2026). Slovensky/Banskobystricky kraj. **Jednota SD** = Spotrebné družstvo Jednota. city Brezno. || TBD: city 'Jednota SD Brezno' → 'Brezno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J492" t="inlineStr">
         <is>
-          <t>Jednota SD Brezno</t>
+          <t>Brezno</t>
         </is>
       </c>
     </row>
@@ -54328,12 +54488,12 @@
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -54575,12 +54735,12 @@
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>Poprad = TJ Štátný majetok Poprad (Wiki D42 - registr ustavy 04/2026). Slovensky/Prešovský kraj. **Štátný majetok** = státní statky. city Poprad.</t>
+          <t>Poprad = TJ Štátný majetok Poprad (Wiki D42 - registr ustavy 04/2026). Slovensky/Prešovský kraj. **Štátný majetok** = státní statky. city Poprad. || TBD: city 'Štátný majetok Poprad' → 'Poprad' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>Štátný majetok Poprad</t>
+          <t>Poprad</t>
         </is>
       </c>
     </row>
@@ -58181,11 +58341,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -58230,21 +58390,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0413</t>
+          <t>CLUB_S1988_89_0007</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0413 'Rájec-Jestřebí' prev→CLUB_S1987_88_0416 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -58252,21 +58410,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0049</t>
+          <t>CLUB_S1988_89_0021</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0049 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -58274,21 +58430,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0050</t>
+          <t>CLUB_S1988_89_0025</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0050 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -58296,21 +58450,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0051</t>
+          <t>CLUB_S1988_89_0027</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0051 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -58318,21 +58470,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0052</t>
+          <t>CLUB_S1988_89_0037</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0052 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -58340,21 +58490,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0053</t>
+          <t>CLUB_S1988_89_0040</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0053 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -58362,21 +58510,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0054</t>
+          <t>CLUB_S1988_89_0065</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0054 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -58384,21 +58530,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0055</t>
+          <t>CLUB_S1988_89_0067</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0055 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -58406,21 +58550,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0056</t>
+          <t>CLUB_S1988_89_0068</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0056 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -58428,21 +58570,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0057</t>
+          <t>CLUB_S1988_89_0069</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0057 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -58450,21 +58590,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0102</t>
+          <t>CLUB_S1988_89_0074</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0102 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -58472,21 +58610,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0103</t>
+          <t>CLUB_S1988_89_0076</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0103 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -58494,21 +58630,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0104</t>
+          <t>CLUB_S1988_89_0088</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0104 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -58516,21 +58650,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0107</t>
+          <t>CLUB_S1988_89_0095</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0107 fate nekonzist. ['setrval', 'setrval?'] → 'setrval' (cross-ref=ne) — ověřit</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -58538,21 +58670,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0108</t>
+          <t>CLUB_S1988_89_0099</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0108 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -58560,21 +58690,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0109</t>
+          <t>CLUB_S1988_89_0101</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0109 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -58582,21 +58710,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0175</t>
+          <t>CLUB_S1988_89_0123</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0175 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -58604,7 +58730,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -58614,11 +58740,9 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0176 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -58626,21 +58750,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0177</t>
+          <t>CLUB_S1988_89_0178</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0177 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -58648,21 +58770,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0178</t>
+          <t>CLUB_S1988_89_0179</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0178 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -58670,21 +58790,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0401</t>
+          <t>CLUB_S1988_89_0180</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0401 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -58692,21 +58810,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0402</t>
+          <t>CLUB_S1988_89_0180</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0402 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -58714,21 +58830,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0403</t>
+          <t>CLUB_S1988_89_0182</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0403 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -58736,21 +58850,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0404</t>
+          <t>CLUB_S1988_89_0189</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0404 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -58758,21 +58870,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0405</t>
+          <t>CLUB_S1988_89_0194</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0405 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -58780,21 +58890,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0406</t>
+          <t>CLUB_S1988_89_0199</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0406 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -58802,21 +58910,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0408</t>
+          <t>CLUB_S1988_89_0201</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0408 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -58824,21 +58930,19 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0409</t>
+          <t>CLUB_S1988_89_0202</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0409 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -58846,21 +58950,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0410</t>
+          <t>CLUB_S1988_89_0205</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0410 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -58868,21 +58970,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0412</t>
+          <t>CLUB_S1988_89_0221</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0412 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1987_88_0216 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -58890,21 +58990,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0413</t>
+          <t>CLUB_S1988_89_0250</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0413 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+          <t>TBD: city 'Kluky' → 'Dražice A' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -58912,21 +59010,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0414</t>
+          <t>CLUB_S1988_89_0265</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0414 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -58934,21 +59030,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0415</t>
+          <t>CLUB_S1988_89_0272</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0415 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Stadion Cheb' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -58956,21 +59050,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0416</t>
+          <t>CLUB_S1988_89_0287</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0416 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -58978,21 +59070,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0418</t>
+          <t>CLUB_S1988_89_0289</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0418 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -59000,21 +59090,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0419</t>
+          <t>CLUB_S1988_89_0294</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0419 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -59022,21 +59110,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0420</t>
+          <t>CLUB_S1988_89_0297</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0420 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>TBD: city 'Centroflor Dolní Pustevna' → 'Dolní Pustevna' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -59044,21 +59130,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0421</t>
+          <t>CLUB_S1988_89_0298</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0421 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -59066,21 +59150,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0422</t>
+          <t>CLUB_S1988_89_0299</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0422 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -59088,21 +59170,19 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0451</t>
+          <t>CLUB_S1988_89_0302</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0451 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -59110,21 +59190,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0452</t>
+          <t>CLUB_S1988_89_0303</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0452 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+          <t>TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -59132,21 +59210,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0453</t>
+          <t>CLUB_S1988_89_0304</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0453 fate nekonzist. ['setrval', 'setrval?'] → 'setrval' (cross-ref=ne) — ověřit</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -59154,21 +59230,19 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0454</t>
+          <t>CLUB_S1988_89_0307</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0454 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -59176,21 +59250,19 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0462</t>
+          <t>CLUB_S1988_89_0312</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0462 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -59198,21 +59270,19 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0463</t>
+          <t>CLUB_S1988_89_0341</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0463 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -59220,21 +59290,19 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0464</t>
+          <t>CLUB_S1988_89_0344</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0464 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -59242,21 +59310,19 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0465</t>
+          <t>CLUB_S1988_89_0358</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0465 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -59264,21 +59330,19 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0466</t>
+          <t>CLUB_S1988_89_0385</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0466 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -59286,21 +59350,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0467</t>
+          <t>CLUB_S1988_89_0390</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0467 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -59308,21 +59370,19 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0468</t>
+          <t>CLUB_S1988_89_0395</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0468 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -59330,21 +59390,19 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0469</t>
+          <t>CLUB_S1988_89_0400</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0469 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -59352,21 +59410,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0470</t>
+          <t>CLUB_S1988_89_0401</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0470 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -59374,21 +59430,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NODE_S1988_89_0002</t>
+          <t>CLUB_S1988_89_0411</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1988_89_0002 'Kvalifikace o 1.CHL' (L15, parent=NODE_S1988_89_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+          <t>TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -59396,24 +59450,242 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NODE_S1988_89_0018</t>
+          <t>CLUB_S1988_89_0412</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1988_89_0018 'Prolínací soutěž' (L15, parent=NODE_S1988_89_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1987_88_0451 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0413</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1987_88_0416 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0422</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0451</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0453</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hutní Montáže Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0455</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0508</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Jednota SD Brezno' → 'Brezno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0514</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>CLUB_S1988_89_0520</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Štátný majetok Poprad' → 'Poprad' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0027</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0028</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0029</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F55"/>
+  <autoFilter ref="A1:F66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1988_89_FINAL.xlsx
+++ b/data/S1988_89_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23740,7 +23740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23822,7 +23822,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -23834,7 +23834,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -23846,7 +23846,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -23858,7 +23858,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -23870,7 +23870,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -23882,7 +23882,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -23894,7 +23894,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -23906,7 +23906,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -23918,7 +23918,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -23930,7 +23930,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -23942,7 +23942,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -23954,7 +23954,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -23966,7 +23966,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -23978,7 +23978,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -23990,7 +23990,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -24002,7 +24002,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -24014,7 +24014,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -24026,7 +24026,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -24050,7 +24050,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -24062,7 +24062,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1987_88_0216 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -24074,7 +24074,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -24086,7 +24086,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -24098,7 +24098,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -24110,7 +24110,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -24122,7 +24122,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Centroflor Dolní Pustevna' → 'Dolní Pustevna' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -24134,7 +24134,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -24146,7 +24146,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -24158,7 +24158,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -24170,7 +24170,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1987_88_0216 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -24182,7 +24182,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kluky' → 'Dražice A' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -24194,7 +24194,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -24206,7 +24206,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Stadion Cheb' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -24218,7 +24218,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -24230,7 +24230,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -24242,7 +24242,7 @@
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -24254,7 +24254,7 @@
     <row r="40">
       <c r="C40" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Centroflor Dolní Pustevna' → 'Dolní Pustevna' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -24266,7 +24266,7 @@
     <row r="41">
       <c r="C41" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -24278,7 +24278,7 @@
     <row r="42">
       <c r="C42" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -24290,7 +24290,7 @@
     <row r="43">
       <c r="C43" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -24302,7 +24302,7 @@
     <row r="44">
       <c r="C44" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -24314,7 +24314,7 @@
     <row r="45">
       <c r="C45" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1987_88_0451 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -24326,7 +24326,7 @@
     <row r="46">
       <c r="C46" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1987_88_0416 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -24338,7 +24338,7 @@
     <row r="47">
       <c r="C47" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -24350,7 +24350,7 @@
     <row r="48">
       <c r="C48" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -24362,7 +24362,7 @@
     <row r="49">
       <c r="C49" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hutní Montáže Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -24374,7 +24374,7 @@
     <row r="50">
       <c r="C50" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Jednota SD Brezno' → 'Brezno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -24386,7 +24386,7 @@
     <row r="51">
       <c r="C51" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -24398,7 +24398,7 @@
     <row r="52">
       <c r="C52" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Štátný majetok Poprad' → 'Poprad' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -24408,9 +24408,14 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0027</t>
+        </is>
+      </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -24420,9 +24425,14 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0028</t>
+        </is>
+      </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -24432,183 +24442,17 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0029</t>
+        </is>
+      </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1987_88_0451 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1987_88_0416 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hutní Montáže Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Jednota SD Brezno' → 'Brezno' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Štátný majetok Poprad' → 'Poprad' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>NODE_S1988_89_0027</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>NODE_S1988_89_0028</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>NODE_S1988_89_0029</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -24625,7 +24469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K149"/>
+  <dimension ref="A1:L149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24684,6 +24528,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24726,6 +24575,11 @@
           <t>12 týmů: základ + playoff + o udržení + prolínací soutěž. Mistr: Tesla Pardubice.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24815,6 +24669,11 @@
           <t>I.ČNHL: základ + playoff (QF/SF/O 3.) + O 5.-8. + O 9.-12. I.SNHL (12). Kvalifikace o 1.CHL samostatnou sérií.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24857,6 +24716,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24899,6 +24763,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24941,6 +24810,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24983,6 +24857,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25025,6 +24904,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25067,6 +24951,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25109,6 +24998,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25151,6 +25045,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -25193,6 +25092,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -25235,6 +25139,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -25277,6 +25186,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -25319,6 +25233,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -25487,6 +25406,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0016</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -25529,6 +25453,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0017</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -25571,6 +25500,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0018</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -25618,6 +25552,11 @@
           <t>Finále se nehrálo. Vítěze 1. ČNHL určily výsledky vzájemných utkání Olomouc – Zetor Brno v prolínací soutěži o 1. CHL.</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0019</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -25660,6 +25599,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0020</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -25707,6 +25651,11 @@
           <t>ASD Dukla Jihlava "B" hrála svá domácí utkání v Táboře.</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0021</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -25801,6 +25750,11 @@
           <t>Kvalifikace o postup do II.ligy</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0023</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -25897,6 +25851,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0026</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -25939,6 +25898,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0030</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -26191,6 +26155,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0034</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -26275,6 +26244,11 @@
           <t>II.ČNHL: 3 skupiny + finále. Z 2. ČNHL sestoupily Sušice a Šumperk (dva poslední s nejméně body).</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0037</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -26317,6 +26291,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0038</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -26359,6 +26338,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0039</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -26401,6 +26385,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0040</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -26443,6 +26432,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0041</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -26485,6 +26479,11 @@
           <t>II.SNHL: červená, bílá, modrá skupina + finálová skupina + tři skupiny o umístění. Před soutěží odstoupil TJ Družstevník Letanovce; TJ Štart Spišská Nová Ves hrál v minulé sezóně jako TJ Štart Teplička.</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0042</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -26527,6 +26526,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0043</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -26569,6 +26573,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0044</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -26653,6 +26662,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0045</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -26821,6 +26835,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0047</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -26952,6 +26971,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0050</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -26994,6 +27018,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0051</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -27120,6 +27149,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0052</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -27246,6 +27280,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0055</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -27288,6 +27327,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0056</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -27461,6 +27505,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0061</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -27503,6 +27552,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0062</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -27587,6 +27641,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0063</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -27629,6 +27688,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0064</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -27671,6 +27735,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0065</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -27760,6 +27829,11 @@
           <t>Kvalifikace o KP</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0067</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -27802,6 +27876,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0068</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -27844,6 +27923,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0069</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -27886,6 +27970,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0070</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -27928,6 +28017,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0071</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -28012,6 +28106,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0073</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -28054,6 +28153,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0074</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -28096,6 +28200,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0075</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -28143,6 +28252,11 @@
           <t>kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0076</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -28185,6 +28299,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0077</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -28227,6 +28346,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0078</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -28395,6 +28519,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0080</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -28437,6 +28566,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0081</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -28479,6 +28613,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0082</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -28521,6 +28660,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0083</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -28605,6 +28749,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0094</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -28647,6 +28796,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0095</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -28689,6 +28843,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0096</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -28731,6 +28890,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0097</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -28773,6 +28937,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0098</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -28815,6 +28984,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0099</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -28857,6 +29031,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0100</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -28941,6 +29120,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0102</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -28983,6 +29167,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0103</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -29025,6 +29214,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0104</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -29067,6 +29261,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0105</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -29408,6 +29607,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0113</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -29450,6 +29654,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0114</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -29492,6 +29701,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0115</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -29618,6 +29832,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0119</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -29660,6 +29879,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0120</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -29702,6 +29926,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0121</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -29826,6 +30055,11 @@
       <c r="J123" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0126</t>
         </is>
       </c>
     </row>
@@ -30227,6 +30461,11 @@
           <t>I.liga (10 týmů, jeden stůl)</t>
         </is>
       </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -30244,6 +30483,11 @@
           <t>NODE_S1988_89_0001</t>
         </is>
       </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -30261,6 +30505,11 @@
           <t>NODE_S1988_89_0003</t>
         </is>
       </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -30278,6 +30527,11 @@
           <t>NODE_S1988_89_0003</t>
         </is>
       </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -30295,6 +30549,11 @@
           <t>NODE_S1988_89_0038</t>
         </is>
       </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -30305,6 +30564,11 @@
       <c r="B141" t="inlineStr">
         <is>
           <t>Okresní přebory (jen registr)</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>okresní</t>
         </is>
       </c>
     </row>
@@ -32753,12 +33017,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -33519,12 +33783,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -33603,12 +33867,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -33944,12 +34208,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Liberec</t>
         </is>
       </c>
     </row>
@@ -39696,12 +39960,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -39822,12 +40086,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -39864,12 +40128,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -39953,12 +40217,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -40267,12 +40531,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -43134,12 +43398,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Kluky u Písku = TJ Sokol Kluky (Wiki D42 - registr ustavy 04/2026). 'Sokol  Kluky' s dvojite mezerou - parsing artifakt. Jihocesky kraj (okres Pisek). city Kluky u Písku. || TBD: city 'Kluky' → 'Dražice A' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Kluky u Písku = TJ Sokol Kluky (Wiki D42 - registr ustavy 04/2026). 'Sokol  Kluky' s dvojite mezerou - parsing artifakt. Jihocesky kraj (okres Pisek). city Kluky u Písku.</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Dražice A</t>
+          <t>Kluky u Písku</t>
         </is>
       </c>
     </row>
@@ -44078,12 +44342,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Stadion Cheb' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>Stadion Cheb</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -49191,12 +49455,12 @@
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>Modeta Jihlava</t>
+          <t>Jihlava</t>
         </is>
       </c>
     </row>
@@ -51982,12 +52246,12 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -58341,7 +58605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -58395,12 +58659,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0007</t>
+          <t>CLUB_S1988_89_0021</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58415,12 +58679,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0021</t>
+          <t>CLUB_S1988_89_0040</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58435,12 +58699,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0025</t>
+          <t>CLUB_S1988_89_0065</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58455,12 +58719,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0027</t>
+          <t>CLUB_S1988_89_0067</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58475,12 +58739,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0037</t>
+          <t>CLUB_S1988_89_0068</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58495,12 +58759,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0040</t>
+          <t>CLUB_S1988_89_0069</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58515,12 +58779,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0065</t>
+          <t>CLUB_S1988_89_0074</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58535,12 +58799,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0067</t>
+          <t>CLUB_S1988_89_0076</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58555,12 +58819,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0068</t>
+          <t>CLUB_S1988_89_0088</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58575,12 +58839,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0069</t>
+          <t>CLUB_S1988_89_0095</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58595,12 +58859,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0074</t>
+          <t>CLUB_S1988_89_0099</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58615,12 +58879,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0076</t>
+          <t>CLUB_S1988_89_0101</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58635,12 +58899,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0088</t>
+          <t>CLUB_S1988_89_0123</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58655,12 +58919,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0095</t>
+          <t>CLUB_S1988_89_0178</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58675,12 +58939,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0099</t>
+          <t>CLUB_S1988_89_0180</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58695,12 +58959,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0101</t>
+          <t>CLUB_S1988_89_0194</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58715,12 +58979,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0123</t>
+          <t>CLUB_S1988_89_0199</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58735,12 +58999,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0176</t>
+          <t>CLUB_S1988_89_0201</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58755,7 +59019,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0178</t>
+          <t>CLUB_S1988_89_0202</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -58775,12 +59039,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0179</t>
+          <t>CLUB_S1988_89_0205</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58795,12 +59059,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0180</t>
+          <t>CLUB_S1988_89_0221</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1987_88_0216 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -58815,12 +59079,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0180</t>
+          <t>CLUB_S1988_89_0265</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58835,12 +59099,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0182</t>
+          <t>CLUB_S1988_89_0287</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58855,12 +59119,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0189</t>
+          <t>CLUB_S1988_89_0289</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58875,12 +59139,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0194</t>
+          <t>CLUB_S1988_89_0294</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58895,12 +59159,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0199</t>
+          <t>CLUB_S1988_89_0297</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Centroflor Dolní Pustevna' → 'Dolní Pustevna' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58915,12 +59179,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0201</t>
+          <t>CLUB_S1988_89_0298</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58935,12 +59199,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0202</t>
+          <t>CLUB_S1988_89_0299</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58955,12 +59219,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0205</t>
+          <t>CLUB_S1988_89_0302</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58975,12 +59239,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0221</t>
+          <t>CLUB_S1988_89_0303</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1987_88_0216 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58995,12 +59259,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0250</t>
+          <t>CLUB_S1988_89_0304</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kluky' → 'Dražice A' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59015,12 +59279,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0265</t>
+          <t>CLUB_S1988_89_0307</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59035,12 +59299,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0272</t>
+          <t>CLUB_S1988_89_0312</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Stadion Cheb' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59055,12 +59319,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0287</t>
+          <t>CLUB_S1988_89_0341</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59075,12 +59339,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0289</t>
+          <t>CLUB_S1988_89_0344</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -59095,12 +59359,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0294</t>
+          <t>CLUB_S1988_89_0358</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -59115,12 +59379,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0297</t>
+          <t>CLUB_S1988_89_0385</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Centroflor Dolní Pustevna' → 'Dolní Pustevna' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
     </row>
@@ -59135,12 +59399,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0298</t>
+          <t>CLUB_S1988_89_0395</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59155,12 +59419,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0299</t>
+          <t>CLUB_S1988_89_0400</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -59175,12 +59439,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0302</t>
+          <t>CLUB_S1988_89_0401</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
     </row>
@@ -59195,12 +59459,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0303</t>
+          <t>CLUB_S1988_89_0411</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59215,12 +59479,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0304</t>
+          <t>CLUB_S1988_89_0412</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1987_88_0451 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -59235,12 +59499,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0307</t>
+          <t>CLUB_S1988_89_0413</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1987_88_0416 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -59255,12 +59519,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0312</t>
+          <t>CLUB_S1988_89_0422</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59275,12 +59539,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0341</t>
+          <t>CLUB_S1988_89_0451</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59295,12 +59559,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0344</t>
+          <t>CLUB_S1988_89_0453</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: city 'Hutní Montáže Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59315,12 +59579,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0358</t>
+          <t>CLUB_S1988_89_0508</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: city 'Jednota SD Brezno' → 'Brezno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59335,12 +59599,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0385</t>
+          <t>CLUB_S1988_89_0514</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59355,12 +59619,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0390</t>
+          <t>CLUB_S1988_89_0520</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Štátný majetok Poprad' → 'Poprad' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59370,17 +59634,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0395</t>
+          <t>NODE_S1988_89_0027</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
         </is>
       </c>
     </row>
@@ -59390,17 +59654,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0400</t>
+          <t>NODE_S1988_89_0028</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>
       </c>
     </row>
@@ -59410,282 +59674,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CLUB_S1988_89_0401</t>
+          <t>NODE_S1988_89_0029</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>CLUB_S1988_89_0411</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>CLUB_S1988_89_0412</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1987_88_0451 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>CLUB_S1988_89_0413</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1987_88_0416 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>CLUB_S1988_89_0422</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>CLUB_S1988_89_0451</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>CLUB_S1988_89_0453</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Hutní Montáže Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>CLUB_S1988_89_0455</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>CLUB_S1988_89_0508</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Jednota SD Brezno' → 'Brezno' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>CLUB_S1988_89_0514</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>CLUB_S1988_89_0520</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Štátný majetok Poprad' → 'Poprad' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>NODE_S1988_89_0027</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>NODE_S1988_89_0028</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>NODE_S1988_89_0029</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F66"/>
+  <autoFilter ref="A1:F53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1988_89_FINAL.xlsx
+++ b/data/S1988_89_FINAL.xlsx
@@ -2651,13 +2651,13 @@
         <v>6</v>
       </c>
       <c r="G41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>13</v>

--- a/data/S1988_89_FINAL.xlsx
+++ b/data/S1988_89_FINAL.xlsx
@@ -57141,7 +57141,7 @@
         <v>43</v>
       </c>
       <c r="M32" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -57219,7 +57219,7 @@
         <v>40</v>
       </c>
       <c r="M33" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -57297,7 +57297,7 @@
         <v>58</v>
       </c>
       <c r="M34" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -57644,7 +57644,7 @@
         <v>11</v>
       </c>
       <c r="J39" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -57652,7 +57652,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="M39" t="n">
         <v>62</v>
@@ -58034,7 +58034,7 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -58042,7 +58042,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M44" t="n">
         <v>39</v>

--- a/data/S1988_89_FINAL.xlsx
+++ b/data/S1988_89_FINAL.xlsx
@@ -24469,7 +24469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L149"/>
+  <dimension ref="A1:N149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24533,6 +24533,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24800,6 +24810,16 @@
           <t>NODE_S1988_89_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0008</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0014</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24814,6 +24834,14 @@
         <is>
           <t>NODE_S1987_88_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>12 týmů, čtyřkolově</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -24894,6 +24922,16 @@
           <t>NODE_S1988_89_0007</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0009</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0017</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24908,6 +24946,14 @@
         <is>
           <t>NODE_S1987_88_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>1.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -24941,6 +24987,16 @@
           <t>NODE_S1988_89_0007</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0013</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0012</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24955,6 +25011,14 @@
         <is>
           <t>NODE_S1987_88_0009</t>
         </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -24988,6 +25052,8 @@
           <t>NODE_S1988_89_0007</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25002,6 +25068,14 @@
         <is>
           <t>NODE_S1987_88_0010</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>poražení sk. 5.–8.</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -25035,6 +25109,8 @@
           <t>NODE_S1988_89_0007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25049,6 +25125,14 @@
         <is>
           <t>NODE_S1987_88_0011</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>vítězové sk. 5.–8.</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -25082,6 +25166,8 @@
           <t>NODE_S1988_89_0007</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25096,6 +25182,14 @@
         <is>
           <t>NODE_S1987_88_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -25129,6 +25223,8 @@
           <t>NODE_S1988_89_0007</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25143,6 +25239,14 @@
         <is>
           <t>NODE_S1987_88_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -25176,6 +25280,12 @@
           <t>NODE_S1988_89_0001</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0016</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25190,6 +25300,14 @@
         <is>
           <t>NODE_S1987_88_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>9.–12. ZČ</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -25270,6 +25388,8 @@
           <t>NODE_S1988_89_0007</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25279,6 +25399,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>sk. o udržení</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -25312,6 +25440,16 @@
           <t>NODE_S1988_89_0007</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0011</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0010</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25321,6 +25459,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">

--- a/data/S1988_89_FINAL.xlsx
+++ b/data/S1988_89_FINAL.xlsx
@@ -24837,7 +24837,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>12 týmů, čtyřkolově</t>
+          <t>12 týmů</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -24953,7 +24953,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -25018,7 +25018,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -25071,11 +25071,11 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>poražení sk. 5.–8.</t>
+          <t>sk. o 5.–8. (dolní)</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -25128,11 +25128,11 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>vítězové sk. 5.–8.</t>
+          <t>sk. o 5.–8. (horní)</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -25189,7 +25189,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -25246,7 +25246,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -25281,11 +25281,7 @@
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>NODE_S1988_89_0016</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25341,6 +25337,8 @@
           <t>NODE_S1988_89_0007</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25355,6 +25353,14 @@
         <is>
           <t>NODE_S1987_88_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -25402,11 +25408,11 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>sk. o udržení</t>
+          <t>o 9. místo</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -25466,7 +25472,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -25542,6 +25548,12 @@
           <t>NODE_S1988_89_0004</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0020</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25556,6 +25568,14 @@
         <is>
           <t>NODE_S1987_88_0016</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -25589,6 +25609,16 @@
           <t>NODE_S1988_89_0004</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0021</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0024</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25603,6 +25633,14 @@
         <is>
           <t>NODE_S1987_88_0017</t>
         </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -25636,6 +25674,16 @@
           <t>NODE_S1988_89_0004</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0022</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0023</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25650,6 +25698,14 @@
         <is>
           <t>NODE_S1987_88_0018</t>
         </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -25683,6 +25739,8 @@
           <t>NODE_S1988_89_0004</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25702,6 +25760,14 @@
         <is>
           <t>NODE_S1987_88_0019</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -25735,6 +25801,8 @@
           <t>NODE_S1988_89_0004</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25749,6 +25817,14 @@
         <is>
           <t>NODE_S1987_88_0020</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -25782,6 +25858,8 @@
           <t>NODE_S1988_89_0004</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25801,6 +25879,14 @@
         <is>
           <t>NODE_S1987_88_0021</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -25834,6 +25920,8 @@
           <t>NODE_S1988_89_0004</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25848,6 +25936,14 @@
         <is>
           <t>Závorky v PDF značí přenesené body / pomocné pořadí.</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -26291,6 +26387,8 @@
           <t>NODE_S1988_89_0030</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26305,6 +26403,14 @@
         <is>
           <t>NODE_S1987_88_0034</t>
         </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -26338,6 +26444,8 @@
           <t>NODE_S1988_89_0030</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26347,6 +26455,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -26568,6 +26684,8 @@
           <t>NODE_S1988_89_0038</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26582,6 +26700,14 @@
         <is>
           <t>NODE_S1987_88_0041</t>
         </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -26798,6 +26924,8 @@
           <t>NODE_S1988_89_0044</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26812,6 +26940,14 @@
         <is>
           <t>NODE_S1987_88_0045</t>
         </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -26845,6 +26981,8 @@
           <t>NODE_S1988_89_0044</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26854,6 +26992,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -26887,6 +27033,8 @@
           <t>NODE_S1988_89_0046</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26896,6 +27044,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -26929,6 +27085,8 @@
           <t>NODE_S1988_89_0046</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26938,6 +27096,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -26971,6 +27137,8 @@
           <t>NODE_S1988_89_0045</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26985,6 +27153,14 @@
         <is>
           <t>NODE_S1987_88_0047</t>
         </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -27018,6 +27194,8 @@
           <t>NODE_S1988_89_0045</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27027,6 +27205,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -27102,6 +27288,12 @@
           <t>REG_STC</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0057</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27121,6 +27313,14 @@
         <is>
           <t>NODE_S1987_88_0050</t>
         </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -27243,6 +27443,8 @@
           <t>NODE_S1988_89_0054</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27252,6 +27454,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>-1.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -27463,6 +27673,8 @@
           <t>NODE_S1988_89_0054</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27477,6 +27689,14 @@
         <is>
           <t>NODE_S1987_88_0056</t>
         </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>-1.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -28106,6 +28326,16 @@
           <t>NODE_S1988_89_0074</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0077</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0078</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28120,6 +28350,14 @@
         <is>
           <t>NODE_S1987_88_0070</t>
         </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -28153,6 +28391,8 @@
           <t>NODE_S1988_89_0074</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28167,6 +28407,14 @@
         <is>
           <t>NODE_S1987_88_0071</t>
         </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -28200,6 +28448,8 @@
           <t>NODE_S1988_89_0074</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28209,6 +28459,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>5.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -28529,6 +28787,16 @@
           <t>NODE_S1988_89_0083</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0086</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0087</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28538,6 +28806,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -28571,6 +28847,8 @@
           <t>NODE_S1988_89_0083</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28580,6 +28858,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="88">
@@ -28613,6 +28899,8 @@
           <t>NODE_S1988_89_0083</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28622,6 +28910,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>7.–10. ZČ</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -28843,6 +29139,8 @@
           <t>NODE_S1988_89_0089</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28852,6 +29150,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="94">
@@ -29073,6 +29379,8 @@
           <t>NODE_S1988_89_0093</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29087,6 +29395,14 @@
         <is>
           <t>NODE_S1987_88_0098</t>
         </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="99">
@@ -29120,6 +29436,8 @@
           <t>NODE_S1988_89_0093</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29134,6 +29452,14 @@
         <is>
           <t>NODE_S1987_88_0099</t>
         </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="100">
@@ -29167,6 +29493,8 @@
           <t>NODE_S1988_89_0093</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29181,6 +29509,14 @@
         <is>
           <t>NODE_S1987_88_0100</t>
         </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="101">
@@ -29528,6 +29864,8 @@
           <t>NODE_S1988_89_0093</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29537,6 +29875,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="109">
@@ -29570,6 +29916,8 @@
           <t>NODE_S1988_89_0093</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29579,6 +29927,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="110">
@@ -29612,6 +29968,8 @@
           <t>NODE_S1988_89_0093</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29621,6 +29979,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="111">
@@ -29654,6 +30020,8 @@
           <t>NODE_S1988_89_0093</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29663,6 +30031,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="112">
@@ -29837,6 +30213,12 @@
           <t>NODE_S1988_89_0112</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0120</t>
+        </is>
+      </c>
       <c r="I115" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29851,6 +30233,14 @@
         <is>
           <t>NODE_S1987_88_0115</t>
         </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -30109,6 +30499,8 @@
           <t>NODE_S1988_89_0112</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30118,6 +30510,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>7.–10. ZČ</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="122">
@@ -30240,6 +30640,12 @@
           <t>NODE_S1988_89_0132</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>NODE_S1988_89_0124</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30249,6 +30655,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -30282,6 +30696,8 @@
           <t>NODE_S1988_89_0132</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30291,6 +30707,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="126">
@@ -30492,6 +30916,8 @@
           <t>NODE_S1988_89_0134</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30501,6 +30927,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="131">
@@ -30534,6 +30968,8 @@
           <t>NODE_S1988_89_0134</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30543,6 +30979,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="132">
@@ -30576,6 +31020,8 @@
           <t>NODE_S1988_89_0134</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30585,6 +31031,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="133"/>

--- a/data/S1988_89_FINAL.xlsx
+++ b/data/S1988_89_FINAL.xlsx
@@ -760,6 +760,11 @@
           <t>Tesla Pardubice</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F5" t="n">
         <v>34</v>
       </c>
@@ -25052,8 +25057,6 @@
           <t>NODE_S1988_89_0007</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25109,8 +25112,6 @@
           <t>NODE_S1988_89_0007</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25166,8 +25167,6 @@
           <t>NODE_S1988_89_0007</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25223,8 +25222,6 @@
           <t>NODE_S1988_89_0007</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25280,8 +25277,6 @@
           <t>NODE_S1988_89_0001</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25337,8 +25332,6 @@
           <t>NODE_S1988_89_0007</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25394,8 +25387,6 @@
           <t>NODE_S1988_89_0007</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25553,7 +25544,6 @@
           <t>NODE_S1988_89_0020</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25739,8 +25729,6 @@
           <t>NODE_S1988_89_0004</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25801,8 +25789,6 @@
           <t>NODE_S1988_89_0004</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25858,8 +25844,6 @@
           <t>NODE_S1988_89_0004</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25920,8 +25904,6 @@
           <t>NODE_S1988_89_0004</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26387,8 +26369,6 @@
           <t>NODE_S1988_89_0030</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26444,8 +26424,6 @@
           <t>NODE_S1988_89_0030</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26684,8 +26662,6 @@
           <t>NODE_S1988_89_0038</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26924,8 +26900,6 @@
           <t>NODE_S1988_89_0044</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26981,8 +26955,6 @@
           <t>NODE_S1988_89_0044</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27033,8 +27005,6 @@
           <t>NODE_S1988_89_0046</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27085,8 +27055,6 @@
           <t>NODE_S1988_89_0046</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27137,8 +27105,6 @@
           <t>NODE_S1988_89_0045</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27194,8 +27160,6 @@
           <t>NODE_S1988_89_0045</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27288,7 +27252,6 @@
           <t>REG_STC</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>NODE_S1988_89_0057</t>
@@ -27443,8 +27406,6 @@
           <t>NODE_S1988_89_0054</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27673,8 +27634,6 @@
           <t>NODE_S1988_89_0054</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28391,8 +28350,6 @@
           <t>NODE_S1988_89_0074</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28448,8 +28405,6 @@
           <t>NODE_S1988_89_0074</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28847,8 +28802,6 @@
           <t>NODE_S1988_89_0083</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28899,8 +28852,6 @@
           <t>NODE_S1988_89_0083</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29139,8 +29090,6 @@
           <t>NODE_S1988_89_0089</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29379,8 +29328,6 @@
           <t>NODE_S1988_89_0093</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29436,8 +29383,6 @@
           <t>NODE_S1988_89_0093</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29493,8 +29438,6 @@
           <t>NODE_S1988_89_0093</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29864,8 +29807,6 @@
           <t>NODE_S1988_89_0093</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29916,8 +29857,6 @@
           <t>NODE_S1988_89_0093</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29968,8 +29907,6 @@
           <t>NODE_S1988_89_0093</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30020,8 +29957,6 @@
           <t>NODE_S1988_89_0093</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30213,7 +30148,6 @@
           <t>NODE_S1988_89_0112</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
           <t>NODE_S1988_89_0120</t>
@@ -30499,8 +30433,6 @@
           <t>NODE_S1988_89_0112</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30645,7 +30577,6 @@
           <t>NODE_S1988_89_0124</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30696,8 +30627,6 @@
           <t>NODE_S1988_89_0132</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30916,8 +30845,6 @@
           <t>NODE_S1988_89_0134</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30968,8 +30895,6 @@
           <t>NODE_S1988_89_0134</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -31020,8 +30945,6 @@
           <t>NODE_S1988_89_0134</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -31041,8 +30964,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="133"/>
-    <row r="134"/>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
@@ -31172,7 +31093,6 @@
         </is>
       </c>
     </row>
-    <row r="142"/>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
@@ -59011,7 +58931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59191,6 +59111,18 @@
       <c r="B15" t="inlineStr">
         <is>
           <t>4 oprav kvalifikačních levelů. Sloupec Q (level) aktualizován.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tesla Pardubice</t>
         </is>
       </c>
     </row>

--- a/data/S1988_89_FINAL.xlsx
+++ b/data/S1988_89_FINAL.xlsx
@@ -30964,6 +30964,8 @@
         <v>4</v>
       </c>
     </row>
+    <row r="133"/>
+    <row r="134"/>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
@@ -31093,6 +31095,7 @@
         </is>
       </c>
     </row>
+    <row r="142"/>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
